--- a/results/final_model_metrics.xlsx
+++ b/results/final_model_metrics.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5281739234924316</v>
+        <v>0.5091187953948975</v>
       </c>
     </row>
   </sheetData>
